--- a/backend/income_details.xlsx
+++ b/backend/income_details.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -444,20 +444,9 @@
         <v>46151.12510416667</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Youtube</v>
-      </c>
-      <c r="B5">
-        <v>9000</v>
-      </c>
-      <c r="C5" s="1">
-        <v>46146.12510416667</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
   </ignoredErrors>
 </worksheet>
 </file>